--- a/ig/DM-SIDOBA/ValueSet-jdv-j391-niveau-diplome-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j391-niveau-diplome-ms.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Niveau de diplôme.</t>
+    <t>Niveau de diplôme permettant d'indiquer le type de formation nécessaire pour occuper un poste dans le monde professionnel.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM-SIDOBA/ValueSet-jdv-j391-niveau-diplome-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j391-niveau-diplome-ms.xlsx
@@ -117,7 +117,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r429-niveau-diplome</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r412-niveau-diplome</t>
   </si>
 </sst>
 </file>
